--- a/calendar_chilean_2024B.xlsx
+++ b/calendar_chilean_2024B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed268546/Dropbox/Mac/Documents/codes/SPOCK_chilean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9511B7BF-11AC-0345-9923-39BDDEADC15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08EDAE8D-F3DB-4E46-AC8D-7EE027E3AFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="500" windowWidth="26180" windowHeight="20840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="31">
   <si>
     <t>Date</t>
   </si>
@@ -111,16 +111,55 @@
   <si>
     <t>no data</t>
   </si>
+  <si>
+    <t>windy</t>
+  </si>
+  <si>
+    <t>cloudy</t>
+  </si>
+  <si>
+    <t>few because cloudy</t>
+  </si>
+  <si>
+    <t>not on server but images taken</t>
+  </si>
+  <si>
+    <t>cloudy, but some images taken</t>
+  </si>
+  <si>
+    <t>SPIRIT</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -178,7 +217,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -239,8 +278,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="44">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -679,21 +724,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color rgb="FF000000"/>
@@ -740,25 +770,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -768,6 +780,30 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -778,9 +814,7 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -791,9 +825,7 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -803,13 +835,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -819,169 +851,194 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="50">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1139,6 +1196,336 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1363,7 +1750,7 @@
     <col min="8" max="8" width="14.5" customWidth="1"/>
     <col min="9" max="9" width="27.33203125" customWidth="1"/>
     <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.1640625" style="48" customWidth="1"/>
+    <col min="11" max="11" width="29" style="43" customWidth="1"/>
     <col min="12" max="12" width="22.33203125" customWidth="1"/>
     <col min="13" max="27" width="10.5" customWidth="1"/>
   </cols>
@@ -1399,7 +1786,7 @@
       <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="40" t="s">
+      <c r="K1" s="57" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1425,16 +1812,16 @@
       <c r="G2" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="49" t="s">
+      <c r="J2" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="58" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1463,13 +1850,13 @@
       <c r="H3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="45"/>
+      <c r="J3" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="19">
@@ -1496,13 +1883,13 @@
       <c r="H4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="55" t="s">
+      <c r="I4" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="45"/>
+      <c r="J4" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19">
@@ -1524,8 +1911,8 @@
       <c r="G5" s="35"/>
       <c r="H5" s="13"/>
       <c r="I5" s="36"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="45"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
@@ -1547,8 +1934,8 @@
       <c r="G6" s="35"/>
       <c r="H6" s="13"/>
       <c r="I6" s="36"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="45"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="59"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
@@ -1570,8 +1957,8 @@
       <c r="G7" s="35"/>
       <c r="H7" s="13"/>
       <c r="I7" s="36"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="45"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="59"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
@@ -1593,8 +1980,8 @@
       <c r="G8" s="35"/>
       <c r="H8" s="13"/>
       <c r="I8" s="36"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="45"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="59"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
@@ -1616,8 +2003,8 @@
       <c r="G9" s="35"/>
       <c r="H9" s="13"/>
       <c r="I9" s="36"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="45"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="59"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
@@ -1644,13 +2031,13 @@
       <c r="H10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="56" t="s">
+      <c r="I10" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="50" t="s">
+      <c r="J10" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="46" t="s">
+      <c r="K10" s="60" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1679,13 +2066,13 @@
       <c r="H11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="56" t="s">
+      <c r="I11" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="45"/>
+      <c r="J11" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="59"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19">
@@ -1712,13 +2099,13 @@
       <c r="H12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="56" t="s">
+      <c r="I12" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="45"/>
+      <c r="J12" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="59"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19">
@@ -1740,8 +2127,8 @@
       <c r="G13" s="35"/>
       <c r="H13" s="13"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="45"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="59"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="19">
@@ -1763,8 +2150,8 @@
       <c r="G14" s="35"/>
       <c r="H14" s="13"/>
       <c r="I14" s="36"/>
-      <c r="J14" s="50"/>
-      <c r="K14" s="45"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="59"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="19">
@@ -1786,8 +2173,8 @@
       <c r="G15" s="35"/>
       <c r="H15" s="13"/>
       <c r="I15" s="36"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="45"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="59"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="19">
@@ -1809,8 +2196,8 @@
       <c r="G16" s="35"/>
       <c r="H16" s="13"/>
       <c r="I16" s="36"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="45"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="59"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="19">
@@ -1832,8 +2219,8 @@
       <c r="G17" s="35"/>
       <c r="H17" s="13"/>
       <c r="I17" s="36"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="45"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="59"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="19">
@@ -1860,13 +2247,13 @@
       <c r="H18" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="57" t="s">
+      <c r="I18" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" s="45"/>
+      <c r="J18" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="59"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="19">
@@ -1893,13 +2280,13 @@
       <c r="H19" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="57" t="s">
+      <c r="I19" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="45"/>
+      <c r="J19" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="59"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="19">
@@ -1926,13 +2313,13 @@
       <c r="H20" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="57" t="s">
+      <c r="I20" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="50" t="s">
+      <c r="J20" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="K20" s="46" t="s">
+      <c r="K20" s="60" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1956,8 +2343,8 @@
       <c r="G21" s="35"/>
       <c r="H21" s="13"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="45"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="59"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19">
@@ -1979,8 +2366,8 @@
       <c r="G22" s="35"/>
       <c r="H22" s="13"/>
       <c r="I22" s="36"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="45"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="59"/>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="19">
@@ -2002,8 +2389,8 @@
       <c r="G23" s="35"/>
       <c r="H23" s="13"/>
       <c r="I23" s="36"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="45"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="59"/>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="19">
@@ -2025,8 +2412,8 @@
       <c r="G24" s="35"/>
       <c r="H24" s="13"/>
       <c r="I24" s="36"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="45"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="59"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19">
@@ -2048,8 +2435,8 @@
       <c r="G25" s="35"/>
       <c r="H25" s="13"/>
       <c r="I25" s="36"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="45"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="59"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="19">
@@ -2076,13 +2463,13 @@
       <c r="H26" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="57" t="s">
+      <c r="I26" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J26" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="45"/>
+      <c r="J26" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="59"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="19">
@@ -2109,13 +2496,13 @@
       <c r="H27" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="57" t="s">
+      <c r="I27" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="45"/>
+      <c r="J27" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="59"/>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="19">
@@ -2142,13 +2529,13 @@
       <c r="H28" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="57" t="s">
+      <c r="I28" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J28" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="45"/>
+      <c r="J28" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="59"/>
     </row>
     <row r="29" spans="1:11" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19">
@@ -2170,8 +2557,8 @@
       <c r="G29" s="35"/>
       <c r="H29" s="13"/>
       <c r="I29" s="36"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="45"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="59"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="19">
@@ -2193,8 +2580,8 @@
       <c r="G30" s="35"/>
       <c r="H30" s="13"/>
       <c r="I30" s="36"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="45"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="59"/>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="19">
@@ -2216,8 +2603,8 @@
       <c r="G31" s="35"/>
       <c r="H31" s="13"/>
       <c r="I31" s="36"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="45"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="59"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="19">
@@ -2239,8 +2626,8 @@
       <c r="G32" s="35"/>
       <c r="H32" s="13"/>
       <c r="I32" s="36"/>
-      <c r="J32" s="51"/>
-      <c r="K32" s="45"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="59"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="19">
@@ -2260,10 +2647,10 @@
       </c>
       <c r="F33" s="29"/>
       <c r="G33" s="35"/>
-      <c r="H33" s="60"/>
+      <c r="H33" s="52"/>
       <c r="I33" s="36"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="45"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="59"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="19">
@@ -2290,13 +2677,13 @@
       <c r="H34" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I34" s="59" t="s">
+      <c r="I34" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="J34" s="50" t="s">
+      <c r="J34" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="K34" s="46" t="s">
+      <c r="K34" s="60" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2322,16 +2709,16 @@
       <c r="G35" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H35" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I35" s="57" t="s">
+      <c r="H35" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J35" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="45"/>
+      <c r="J35" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="59"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="19">
@@ -2355,16 +2742,16 @@
       <c r="G36" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H36" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I36" s="57" t="s">
+      <c r="H36" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J36" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" s="45"/>
+      <c r="J36" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="59"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="19">
@@ -2386,8 +2773,8 @@
       <c r="G37" s="35"/>
       <c r="H37" s="13"/>
       <c r="I37" s="36"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="45"/>
+      <c r="J37" s="54"/>
+      <c r="K37" s="59"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="19">
@@ -2409,8 +2796,8 @@
       <c r="G38" s="35"/>
       <c r="H38" s="13"/>
       <c r="I38" s="36"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="45"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="59"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="19">
@@ -2432,8 +2819,8 @@
       <c r="G39" s="35"/>
       <c r="H39" s="13"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="45"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="59"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="19">
@@ -2455,8 +2842,8 @@
       <c r="G40" s="35"/>
       <c r="H40" s="13"/>
       <c r="I40" s="36"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="45"/>
+      <c r="J40" s="54"/>
+      <c r="K40" s="59"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="19">
@@ -2478,8 +2865,8 @@
       <c r="G41" s="35"/>
       <c r="H41" s="13"/>
       <c r="I41" s="36"/>
-      <c r="J41" s="51"/>
-      <c r="K41" s="45"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="59"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="19">
@@ -2503,16 +2890,16 @@
       <c r="G42" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H42" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I42" s="57" t="s">
+      <c r="H42" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J42" s="50" t="s">
+      <c r="J42" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="K42" s="46" t="s">
+      <c r="K42" s="60" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2538,16 +2925,16 @@
       <c r="G43" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H43" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I43" s="57" t="s">
+      <c r="H43" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J43" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="45"/>
+      <c r="J43" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="59"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="19">
@@ -2571,16 +2958,16 @@
       <c r="G44" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H44" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I44" s="57" t="s">
+      <c r="H44" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J44" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="45"/>
+      <c r="J44" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="59"/>
     </row>
     <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="19">
@@ -2602,8 +2989,8 @@
       <c r="G45" s="35"/>
       <c r="H45" s="13"/>
       <c r="I45" s="36"/>
-      <c r="J45" s="51"/>
-      <c r="K45" s="45"/>
+      <c r="J45" s="55"/>
+      <c r="K45" s="59"/>
     </row>
     <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="19">
@@ -2625,8 +3012,8 @@
       <c r="G46" s="35"/>
       <c r="H46" s="13"/>
       <c r="I46" s="36"/>
-      <c r="J46" s="51"/>
-      <c r="K46" s="45"/>
+      <c r="J46" s="55"/>
+      <c r="K46" s="59"/>
     </row>
     <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="19">
@@ -2648,8 +3035,8 @@
       <c r="G47" s="35"/>
       <c r="H47" s="13"/>
       <c r="I47" s="36"/>
-      <c r="J47" s="50"/>
-      <c r="K47" s="45"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="59"/>
     </row>
     <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="19">
@@ -2671,8 +3058,8 @@
       <c r="G48" s="35"/>
       <c r="H48" s="13"/>
       <c r="I48" s="36"/>
-      <c r="J48" s="50"/>
-      <c r="K48" s="45"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="59"/>
     </row>
     <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="19">
@@ -2694,8 +3081,8 @@
       <c r="G49" s="35"/>
       <c r="H49" s="13"/>
       <c r="I49" s="36"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="45"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="59"/>
     </row>
     <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="19">
@@ -2719,16 +3106,16 @@
       <c r="G50" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H50" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I50" s="57" t="s">
+      <c r="H50" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J50" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K50" s="46"/>
+      <c r="J50" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" s="60"/>
     </row>
     <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="19">
@@ -2752,16 +3139,16 @@
       <c r="G51" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H51" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I51" s="57" t="s">
+      <c r="H51" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J51" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K51" s="46"/>
+      <c r="J51" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="60"/>
     </row>
     <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="19">
@@ -2785,16 +3172,16 @@
       <c r="G52" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H52" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I52" s="57" t="s">
+      <c r="H52" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J52" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K52" s="46"/>
+      <c r="J52" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" s="60"/>
     </row>
     <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="19">
@@ -2816,8 +3203,8 @@
       <c r="G53" s="35"/>
       <c r="H53" s="13"/>
       <c r="I53" s="36"/>
-      <c r="J53" s="51"/>
-      <c r="K53" s="45"/>
+      <c r="J53" s="55"/>
+      <c r="K53" s="59"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="19">
@@ -2839,8 +3226,8 @@
       <c r="G54" s="35"/>
       <c r="H54" s="13"/>
       <c r="I54" s="36"/>
-      <c r="J54" s="51"/>
-      <c r="K54" s="45"/>
+      <c r="J54" s="55"/>
+      <c r="K54" s="59"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="19">
@@ -2862,8 +3249,8 @@
       <c r="G55" s="35"/>
       <c r="H55" s="13"/>
       <c r="I55" s="36"/>
-      <c r="J55" s="51"/>
-      <c r="K55" s="45"/>
+      <c r="J55" s="55"/>
+      <c r="K55" s="59"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19">
@@ -2885,8 +3272,8 @@
       <c r="G56" s="35"/>
       <c r="H56" s="13"/>
       <c r="I56" s="36"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="45"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="59"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="19">
@@ -2908,8 +3295,8 @@
       <c r="G57" s="35"/>
       <c r="H57" s="13"/>
       <c r="I57" s="36"/>
-      <c r="J57" s="50"/>
-      <c r="K57" s="45"/>
+      <c r="J57" s="54"/>
+      <c r="K57" s="59"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="19">
@@ -2936,13 +3323,13 @@
       <c r="H58" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I58" s="59" t="s">
+      <c r="I58" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="J58" s="50" t="s">
+      <c r="J58" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="K58" s="46" t="s">
+      <c r="K58" s="60" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2971,13 +3358,13 @@
       <c r="H59" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I59" s="59" t="s">
+      <c r="I59" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="J59" s="50" t="s">
+      <c r="J59" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="K59" s="46" t="s">
+      <c r="K59" s="60" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3003,16 +3390,16 @@
       <c r="G60" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H60" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I60" s="57" t="s">
+      <c r="H60" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J60" s="50" t="s">
+      <c r="J60" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="K60" s="46" t="s">
+      <c r="K60" s="60" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3036,8 +3423,8 @@
       <c r="G61" s="35"/>
       <c r="H61" s="13"/>
       <c r="I61" s="36"/>
-      <c r="J61" s="51"/>
-      <c r="K61" s="45"/>
+      <c r="J61" s="55"/>
+      <c r="K61" s="59"/>
     </row>
     <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="19">
@@ -3059,8 +3446,8 @@
       <c r="G62" s="35"/>
       <c r="H62" s="13"/>
       <c r="I62" s="36"/>
-      <c r="J62" s="51"/>
-      <c r="K62" s="45"/>
+      <c r="J62" s="55"/>
+      <c r="K62" s="59"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="19">
@@ -3082,8 +3469,8 @@
       <c r="G63" s="35"/>
       <c r="H63" s="13"/>
       <c r="I63" s="36"/>
-      <c r="J63" s="51"/>
-      <c r="K63" s="45"/>
+      <c r="J63" s="55"/>
+      <c r="K63" s="59"/>
     </row>
     <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="19">
@@ -3105,8 +3492,8 @@
       <c r="G64" s="35"/>
       <c r="H64" s="13"/>
       <c r="I64" s="36"/>
-      <c r="J64" s="51"/>
-      <c r="K64" s="45"/>
+      <c r="J64" s="55"/>
+      <c r="K64" s="59"/>
     </row>
     <row r="65" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="19">
@@ -3130,16 +3517,16 @@
       <c r="G65" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H65" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I65" s="57" t="s">
+      <c r="H65" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I65" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J65" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K65" s="45"/>
+      <c r="J65" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K65" s="59"/>
     </row>
     <row r="66" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="19">
@@ -3163,16 +3550,16 @@
       <c r="G66" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H66" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I66" s="57" t="s">
+      <c r="H66" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J66" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K66" s="45"/>
+      <c r="J66" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66" s="59"/>
     </row>
     <row r="67" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="19">
@@ -3196,16 +3583,16 @@
       <c r="G67" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H67" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I67" s="57" t="s">
+      <c r="H67" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J67" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K67" s="45"/>
+      <c r="J67" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K67" s="59"/>
     </row>
     <row r="68" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="19">
@@ -3227,8 +3614,8 @@
       <c r="G68" s="35"/>
       <c r="H68" s="13"/>
       <c r="I68" s="36"/>
-      <c r="J68" s="51"/>
-      <c r="K68" s="45"/>
+      <c r="J68" s="55"/>
+      <c r="K68" s="59"/>
     </row>
     <row r="69" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="19">
@@ -3250,8 +3637,8 @@
       <c r="G69" s="35"/>
       <c r="H69" s="13"/>
       <c r="I69" s="36"/>
-      <c r="J69" s="51"/>
-      <c r="K69" s="45"/>
+      <c r="J69" s="55"/>
+      <c r="K69" s="59"/>
     </row>
     <row r="70" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="19">
@@ -3273,8 +3660,8 @@
       <c r="G70" s="35"/>
       <c r="H70" s="13"/>
       <c r="I70" s="36"/>
-      <c r="J70" s="51"/>
-      <c r="K70" s="45"/>
+      <c r="J70" s="55"/>
+      <c r="K70" s="59"/>
     </row>
     <row r="71" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="19">
@@ -3296,8 +3683,8 @@
       <c r="G71" s="35"/>
       <c r="H71" s="13"/>
       <c r="I71" s="36"/>
-      <c r="J71" s="51"/>
-      <c r="K71" s="45"/>
+      <c r="J71" s="55"/>
+      <c r="K71" s="59"/>
     </row>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="19">
@@ -3319,8 +3706,8 @@
       <c r="G72" s="35"/>
       <c r="H72" s="13"/>
       <c r="I72" s="36"/>
-      <c r="J72" s="51"/>
-      <c r="K72" s="45"/>
+      <c r="J72" s="55"/>
+      <c r="K72" s="59"/>
     </row>
     <row r="73" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="19">
@@ -3344,16 +3731,16 @@
       <c r="G73" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H73" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I73" s="57" t="s">
+      <c r="H73" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J73" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K73" s="45"/>
+      <c r="J73" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K73" s="59"/>
     </row>
     <row r="74" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="19">
@@ -3377,16 +3764,16 @@
       <c r="G74" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H74" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I74" s="57" t="s">
+      <c r="H74" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J74" s="50" t="s">
+      <c r="J74" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="K74" s="46" t="s">
+      <c r="K74" s="60" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3412,16 +3799,16 @@
       <c r="G75" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H75" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I75" s="57" t="s">
+      <c r="H75" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I75" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J75" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K75" s="45"/>
+      <c r="J75" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K75" s="59"/>
     </row>
     <row r="76" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="19">
@@ -3443,8 +3830,8 @@
       <c r="G76" s="35"/>
       <c r="H76" s="13"/>
       <c r="I76" s="36"/>
-      <c r="J76" s="50"/>
-      <c r="K76" s="45"/>
+      <c r="J76" s="54"/>
+      <c r="K76" s="59"/>
     </row>
     <row r="77" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="19">
@@ -3466,8 +3853,8 @@
       <c r="G77" s="35"/>
       <c r="H77" s="13"/>
       <c r="I77" s="36"/>
-      <c r="J77" s="51"/>
-      <c r="K77" s="45"/>
+      <c r="J77" s="55"/>
+      <c r="K77" s="59"/>
     </row>
     <row r="78" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="19">
@@ -3489,8 +3876,8 @@
       <c r="G78" s="35"/>
       <c r="H78" s="13"/>
       <c r="I78" s="36"/>
-      <c r="J78" s="51"/>
-      <c r="K78" s="45"/>
+      <c r="J78" s="55"/>
+      <c r="K78" s="59"/>
     </row>
     <row r="79" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="19">
@@ -3512,8 +3899,8 @@
       <c r="G79" s="35"/>
       <c r="H79" s="13"/>
       <c r="I79" s="36"/>
-      <c r="J79" s="51"/>
-      <c r="K79" s="45"/>
+      <c r="J79" s="55"/>
+      <c r="K79" s="59"/>
     </row>
     <row r="80" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="19">
@@ -3535,8 +3922,8 @@
       <c r="G80" s="35"/>
       <c r="H80" s="13"/>
       <c r="I80" s="36"/>
-      <c r="J80" s="51"/>
-      <c r="K80" s="45"/>
+      <c r="J80" s="55"/>
+      <c r="K80" s="59"/>
     </row>
     <row r="81" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="19">
@@ -3560,14 +3947,16 @@
       <c r="G81" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H81" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I81" s="57" t="s">
+      <c r="H81" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J81" s="50"/>
-      <c r="K81" s="45"/>
+      <c r="J81" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K81" s="59"/>
     </row>
     <row r="82" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="19">
@@ -3591,14 +3980,16 @@
       <c r="G82" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H82" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I82" s="57" t="s">
+      <c r="H82" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I82" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J82" s="51"/>
-      <c r="K82" s="45"/>
+      <c r="J82" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K82" s="61"/>
     </row>
     <row r="83" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="19">
@@ -3622,14 +4013,16 @@
       <c r="G83" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H83" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I83" s="57" t="s">
+      <c r="H83" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J83" s="50"/>
-      <c r="K83" s="45"/>
+      <c r="J83" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K83" s="59"/>
     </row>
     <row r="84" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="19">
@@ -3651,8 +4044,8 @@
       <c r="G84" s="35"/>
       <c r="H84" s="13"/>
       <c r="I84" s="36"/>
-      <c r="J84" s="50"/>
-      <c r="K84" s="45"/>
+      <c r="J84" s="54"/>
+      <c r="K84" s="59"/>
     </row>
     <row r="85" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="19">
@@ -3674,8 +4067,8 @@
       <c r="G85" s="35"/>
       <c r="H85" s="13"/>
       <c r="I85" s="36"/>
-      <c r="J85" s="50"/>
-      <c r="K85" s="45"/>
+      <c r="J85" s="54"/>
+      <c r="K85" s="59"/>
     </row>
     <row r="86" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="19">
@@ -3697,8 +4090,8 @@
       <c r="G86" s="35"/>
       <c r="H86" s="13"/>
       <c r="I86" s="36"/>
-      <c r="J86" s="51"/>
-      <c r="K86" s="45"/>
+      <c r="J86" s="55"/>
+      <c r="K86" s="59"/>
     </row>
     <row r="87" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="19">
@@ -3720,8 +4113,8 @@
       <c r="G87" s="35"/>
       <c r="H87" s="13"/>
       <c r="I87" s="36"/>
-      <c r="J87" s="51"/>
-      <c r="K87" s="45"/>
+      <c r="J87" s="55"/>
+      <c r="K87" s="59"/>
     </row>
     <row r="88" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="19">
@@ -3743,8 +4136,8 @@
       <c r="G88" s="35"/>
       <c r="H88" s="13"/>
       <c r="I88" s="36"/>
-      <c r="J88" s="51"/>
-      <c r="K88" s="45"/>
+      <c r="J88" s="55"/>
+      <c r="K88" s="59"/>
     </row>
     <row r="89" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="19">
@@ -3768,14 +4161,18 @@
       <c r="G89" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H89" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I89" s="57" t="s">
+      <c r="H89" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J89" s="50"/>
-      <c r="K89" s="45"/>
+      <c r="J89" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K89" s="60" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="90" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="19">
@@ -3799,14 +4196,18 @@
       <c r="G90" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H90" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I90" s="57" t="s">
+      <c r="H90" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I90" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J90" s="50"/>
-      <c r="K90" s="45"/>
+      <c r="J90" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K90" s="60" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="91" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="19">
@@ -3830,14 +4231,18 @@
       <c r="G91" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H91" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I91" s="57" t="s">
+      <c r="H91" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J91" s="50"/>
-      <c r="K91" s="45"/>
+      <c r="J91" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K91" s="60" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="92" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="19">
@@ -3859,8 +4264,8 @@
       <c r="G92" s="35"/>
       <c r="H92" s="13"/>
       <c r="I92" s="36"/>
-      <c r="J92" s="51"/>
-      <c r="K92" s="45"/>
+      <c r="J92" s="55"/>
+      <c r="K92" s="59"/>
     </row>
     <row r="93" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="19">
@@ -3882,8 +4287,8 @@
       <c r="G93" s="35"/>
       <c r="H93" s="13"/>
       <c r="I93" s="36"/>
-      <c r="J93" s="51"/>
-      <c r="K93" s="45"/>
+      <c r="J93" s="55"/>
+      <c r="K93" s="59"/>
     </row>
     <row r="94" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="19">
@@ -3905,8 +4310,8 @@
       <c r="G94" s="35"/>
       <c r="H94" s="13"/>
       <c r="I94" s="36"/>
-      <c r="J94" s="51"/>
-      <c r="K94" s="45"/>
+      <c r="J94" s="55"/>
+      <c r="K94" s="59"/>
     </row>
     <row r="95" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="19">
@@ -3928,8 +4333,8 @@
       <c r="G95" s="35"/>
       <c r="H95" s="13"/>
       <c r="I95" s="36"/>
-      <c r="J95" s="51"/>
-      <c r="K95" s="45"/>
+      <c r="J95" s="55"/>
+      <c r="K95" s="59"/>
     </row>
     <row r="96" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="19">
@@ -3951,8 +4356,8 @@
       <c r="G96" s="35"/>
       <c r="H96" s="13"/>
       <c r="I96" s="36"/>
-      <c r="J96" s="51"/>
-      <c r="K96" s="45"/>
+      <c r="J96" s="55"/>
+      <c r="K96" s="59"/>
     </row>
     <row r="97" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="19">
@@ -3976,14 +4381,16 @@
       <c r="G97" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H97" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I97" s="57" t="s">
+      <c r="H97" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I97" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J97" s="50"/>
-      <c r="K97" s="45"/>
+      <c r="J97" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K97" s="59"/>
     </row>
     <row r="98" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="19">
@@ -4007,14 +4414,16 @@
       <c r="G98" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H98" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I98" s="57" t="s">
+      <c r="H98" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I98" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J98" s="50"/>
-      <c r="K98" s="45"/>
+      <c r="J98" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K98" s="59"/>
     </row>
     <row r="99" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="19">
@@ -4038,14 +4447,18 @@
       <c r="G99" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H99" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I99" s="57" t="s">
+      <c r="H99" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J99" s="50"/>
-      <c r="K99" s="45"/>
+      <c r="J99" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K99" s="61" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="100" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="19">
@@ -4067,8 +4480,8 @@
       <c r="G100" s="35"/>
       <c r="H100" s="13"/>
       <c r="I100" s="36"/>
-      <c r="J100" s="51"/>
-      <c r="K100" s="45"/>
+      <c r="J100" s="55"/>
+      <c r="K100" s="59"/>
     </row>
     <row r="101" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="19">
@@ -4090,8 +4503,8 @@
       <c r="G101" s="35"/>
       <c r="H101" s="13"/>
       <c r="I101" s="36"/>
-      <c r="J101" s="51"/>
-      <c r="K101" s="45"/>
+      <c r="J101" s="55"/>
+      <c r="K101" s="59"/>
     </row>
     <row r="102" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="19">
@@ -4113,8 +4526,8 @@
       <c r="G102" s="35"/>
       <c r="H102" s="13"/>
       <c r="I102" s="36"/>
-      <c r="J102" s="51"/>
-      <c r="K102" s="45"/>
+      <c r="J102" s="55"/>
+      <c r="K102" s="59"/>
     </row>
     <row r="103" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="19">
@@ -4136,8 +4549,8 @@
       <c r="G103" s="35"/>
       <c r="H103" s="13"/>
       <c r="I103" s="36"/>
-      <c r="J103" s="51"/>
-      <c r="K103" s="45"/>
+      <c r="J103" s="55"/>
+      <c r="K103" s="59"/>
     </row>
     <row r="104" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="19">
@@ -4159,8 +4572,8 @@
       <c r="G104" s="35"/>
       <c r="H104" s="13"/>
       <c r="I104" s="36"/>
-      <c r="J104" s="51"/>
-      <c r="K104" s="45"/>
+      <c r="J104" s="55"/>
+      <c r="K104" s="59"/>
     </row>
     <row r="105" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="19">
@@ -4184,14 +4597,16 @@
       <c r="G105" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H105" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I105" s="57" t="s">
+      <c r="H105" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I105" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J105" s="50"/>
-      <c r="K105" s="45"/>
+      <c r="J105" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K105" s="59"/>
     </row>
     <row r="106" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="19">
@@ -4215,14 +4630,16 @@
       <c r="G106" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H106" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I106" s="57" t="s">
+      <c r="H106" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J106" s="50"/>
-      <c r="K106" s="45"/>
+      <c r="J106" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K106" s="59"/>
     </row>
     <row r="107" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="19">
@@ -4246,14 +4663,16 @@
       <c r="G107" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H107" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="I107" s="57" t="s">
+      <c r="H107" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J107" s="50"/>
-      <c r="K107" s="45"/>
+      <c r="J107" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K107" s="59"/>
     </row>
     <row r="108" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="19">
@@ -4275,8 +4694,8 @@
       <c r="G108" s="35"/>
       <c r="H108" s="13"/>
       <c r="I108" s="36"/>
-      <c r="J108" s="51"/>
-      <c r="K108" s="45"/>
+      <c r="J108" s="55"/>
+      <c r="K108" s="59"/>
     </row>
     <row r="109" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="19">
@@ -4298,8 +4717,8 @@
       <c r="G109" s="35"/>
       <c r="H109" s="13"/>
       <c r="I109" s="36"/>
-      <c r="J109" s="51"/>
-      <c r="K109" s="45"/>
+      <c r="J109" s="55"/>
+      <c r="K109" s="59"/>
     </row>
     <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="19">
@@ -4321,8 +4740,8 @@
       <c r="G110" s="35"/>
       <c r="H110" s="13"/>
       <c r="I110" s="36"/>
-      <c r="J110" s="51"/>
-      <c r="K110" s="45"/>
+      <c r="J110" s="55"/>
+      <c r="K110" s="59"/>
     </row>
     <row r="111" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="19">
@@ -4344,8 +4763,8 @@
       <c r="G111" s="35"/>
       <c r="H111" s="13"/>
       <c r="I111" s="36"/>
-      <c r="J111" s="51"/>
-      <c r="K111" s="45"/>
+      <c r="J111" s="55"/>
+      <c r="K111" s="59"/>
     </row>
     <row r="112" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="19">
@@ -4367,8 +4786,8 @@
       <c r="G112" s="35"/>
       <c r="H112" s="13"/>
       <c r="I112" s="36"/>
-      <c r="J112" s="51"/>
-      <c r="K112" s="45"/>
+      <c r="J112" s="55"/>
+      <c r="K112" s="59"/>
     </row>
     <row r="113" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="19">
@@ -4392,12 +4811,18 @@
       <c r="G113" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H113" s="13"/>
-      <c r="I113" s="57" t="s">
+      <c r="H113" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J113" s="50"/>
-      <c r="K113" s="45"/>
+      <c r="J113" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K113" s="61" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="114" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="19">
@@ -4421,12 +4846,16 @@
       <c r="G114" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H114" s="13"/>
-      <c r="I114" s="57" t="s">
+      <c r="H114" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J114" s="50"/>
-      <c r="K114" s="45"/>
+      <c r="J114" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K114" s="59"/>
     </row>
     <row r="115" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="19">
@@ -4450,10 +4879,18 @@
       <c r="G115" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H115" s="13"/>
-      <c r="I115" s="36"/>
-      <c r="J115" s="50"/>
-      <c r="K115" s="45"/>
+      <c r="H115" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K115" s="61" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="116" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="19">
@@ -4475,8 +4912,8 @@
       <c r="G116" s="35"/>
       <c r="H116" s="13"/>
       <c r="I116" s="36"/>
-      <c r="J116" s="51"/>
-      <c r="K116" s="45"/>
+      <c r="J116" s="55"/>
+      <c r="K116" s="59"/>
     </row>
     <row r="117" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="19">
@@ -4498,8 +4935,8 @@
       <c r="G117" s="35"/>
       <c r="H117" s="13"/>
       <c r="I117" s="36"/>
-      <c r="J117" s="51"/>
-      <c r="K117" s="45"/>
+      <c r="J117" s="55"/>
+      <c r="K117" s="59"/>
     </row>
     <row r="118" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="19">
@@ -4521,8 +4958,8 @@
       <c r="G118" s="35"/>
       <c r="H118" s="13"/>
       <c r="I118" s="36"/>
-      <c r="J118" s="51"/>
-      <c r="K118" s="45"/>
+      <c r="J118" s="55"/>
+      <c r="K118" s="59"/>
     </row>
     <row r="119" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="19">
@@ -4544,8 +4981,8 @@
       <c r="G119" s="35"/>
       <c r="H119" s="13"/>
       <c r="I119" s="36"/>
-      <c r="J119" s="51"/>
-      <c r="K119" s="45"/>
+      <c r="J119" s="55"/>
+      <c r="K119" s="59"/>
     </row>
     <row r="120" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="19">
@@ -4567,8 +5004,8 @@
       <c r="G120" s="35"/>
       <c r="H120" s="13"/>
       <c r="I120" s="36"/>
-      <c r="J120" s="51"/>
-      <c r="K120" s="45"/>
+      <c r="J120" s="55"/>
+      <c r="K120" s="59"/>
     </row>
     <row r="121" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="19">
@@ -4592,10 +5029,16 @@
       <c r="G121" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H121" s="13"/>
-      <c r="I121" s="36"/>
-      <c r="J121" s="50"/>
-      <c r="K121" s="45"/>
+      <c r="H121" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K121" s="59"/>
     </row>
     <row r="122" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="19">
@@ -4619,10 +5062,16 @@
       <c r="G122" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H122" s="13"/>
-      <c r="I122" s="36"/>
-      <c r="J122" s="50"/>
-      <c r="K122" s="45"/>
+      <c r="H122" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K122" s="59"/>
     </row>
     <row r="123" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="19">
@@ -4646,10 +5095,16 @@
       <c r="G123" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H123" s="13"/>
-      <c r="I123" s="36"/>
-      <c r="J123" s="50"/>
-      <c r="K123" s="45"/>
+      <c r="H123" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I123" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J123" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K123" s="59"/>
     </row>
     <row r="124" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="19">
@@ -4671,8 +5126,8 @@
       <c r="G124" s="35"/>
       <c r="H124" s="13"/>
       <c r="I124" s="36"/>
-      <c r="J124" s="51"/>
-      <c r="K124" s="45"/>
+      <c r="J124" s="55"/>
+      <c r="K124" s="59"/>
     </row>
     <row r="125" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="19">
@@ -4694,8 +5149,8 @@
       <c r="G125" s="35"/>
       <c r="H125" s="13"/>
       <c r="I125" s="36"/>
-      <c r="J125" s="51"/>
-      <c r="K125" s="45"/>
+      <c r="J125" s="55"/>
+      <c r="K125" s="59"/>
     </row>
     <row r="126" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="19">
@@ -4717,8 +5172,8 @@
       <c r="G126" s="35"/>
       <c r="H126" s="13"/>
       <c r="I126" s="36"/>
-      <c r="J126" s="51"/>
-      <c r="K126" s="45"/>
+      <c r="J126" s="55"/>
+      <c r="K126" s="59"/>
     </row>
     <row r="127" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="19">
@@ -4740,8 +5195,8 @@
       <c r="G127" s="35"/>
       <c r="H127" s="13"/>
       <c r="I127" s="36"/>
-      <c r="J127" s="51"/>
-      <c r="K127" s="45"/>
+      <c r="J127" s="55"/>
+      <c r="K127" s="59"/>
     </row>
     <row r="128" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="19">
@@ -4763,8 +5218,8 @@
       <c r="G128" s="35"/>
       <c r="H128" s="13"/>
       <c r="I128" s="36"/>
-      <c r="J128" s="51"/>
-      <c r="K128" s="45"/>
+      <c r="J128" s="55"/>
+      <c r="K128" s="59"/>
     </row>
     <row r="129" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="19">
@@ -4788,10 +5243,18 @@
       <c r="G129" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H129" s="13"/>
-      <c r="I129" s="36"/>
-      <c r="J129" s="50"/>
-      <c r="K129" s="45"/>
+      <c r="H129" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K129" s="63" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="130" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="19">
@@ -4815,10 +5278,18 @@
       <c r="G130" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H130" s="13"/>
-      <c r="I130" s="36"/>
-      <c r="J130" s="50"/>
-      <c r="K130" s="45"/>
+      <c r="H130" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J130" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K130" s="63" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="131" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="19">
@@ -4842,10 +5313,18 @@
       <c r="G131" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H131" s="13"/>
-      <c r="I131" s="36"/>
-      <c r="J131" s="50"/>
-      <c r="K131" s="45"/>
+      <c r="H131" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K131" s="63" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="132" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="19">
@@ -4867,8 +5346,8 @@
       <c r="G132" s="35"/>
       <c r="H132" s="13"/>
       <c r="I132" s="36"/>
-      <c r="J132" s="51"/>
-      <c r="K132" s="45"/>
+      <c r="J132" s="55"/>
+      <c r="K132" s="59"/>
     </row>
     <row r="133" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="19">
@@ -4890,8 +5369,8 @@
       <c r="G133" s="35"/>
       <c r="H133" s="13"/>
       <c r="I133" s="36"/>
-      <c r="J133" s="51"/>
-      <c r="K133" s="45"/>
+      <c r="J133" s="55"/>
+      <c r="K133" s="59"/>
     </row>
     <row r="134" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="19">
@@ -4913,8 +5392,8 @@
       <c r="G134" s="35"/>
       <c r="H134" s="13"/>
       <c r="I134" s="36"/>
-      <c r="J134" s="51"/>
-      <c r="K134" s="45"/>
+      <c r="J134" s="55"/>
+      <c r="K134" s="59"/>
     </row>
     <row r="135" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="19">
@@ -4936,8 +5415,8 @@
       <c r="G135" s="35"/>
       <c r="H135" s="13"/>
       <c r="I135" s="36"/>
-      <c r="J135" s="51"/>
-      <c r="K135" s="45"/>
+      <c r="J135" s="55"/>
+      <c r="K135" s="59"/>
     </row>
     <row r="136" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="19">
@@ -4959,8 +5438,8 @@
       <c r="G136" s="35"/>
       <c r="H136" s="13"/>
       <c r="I136" s="36"/>
-      <c r="J136" s="51"/>
-      <c r="K136" s="45"/>
+      <c r="J136" s="55"/>
+      <c r="K136" s="59"/>
     </row>
     <row r="137" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="19">
@@ -4981,11 +5460,21 @@
       <c r="F137" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="G137" s="35"/>
-      <c r="H137" s="13"/>
-      <c r="I137" s="36"/>
-      <c r="J137" s="50"/>
-      <c r="K137" s="45"/>
+      <c r="G137" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H137" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K137" s="63" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="138" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="19">
@@ -5006,11 +5495,19 @@
       <c r="F138" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="G138" s="35"/>
-      <c r="H138" s="13"/>
-      <c r="I138" s="36"/>
-      <c r="J138" s="50"/>
-      <c r="K138" s="45"/>
+      <c r="G138" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H138" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K138" s="59"/>
     </row>
     <row r="139" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="19">
@@ -5031,11 +5528,19 @@
       <c r="F139" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="G139" s="35"/>
-      <c r="H139" s="13"/>
-      <c r="I139" s="36"/>
-      <c r="J139" s="50"/>
-      <c r="K139" s="45"/>
+      <c r="G139" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H139" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J139" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K139" s="59"/>
     </row>
     <row r="140" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="19">
@@ -5057,8 +5562,8 @@
       <c r="G140" s="35"/>
       <c r="H140" s="13"/>
       <c r="I140" s="36"/>
-      <c r="J140" s="51"/>
-      <c r="K140" s="45"/>
+      <c r="J140" s="55"/>
+      <c r="K140" s="59"/>
     </row>
     <row r="141" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="19">
@@ -5080,8 +5585,8 @@
       <c r="G141" s="35"/>
       <c r="H141" s="13"/>
       <c r="I141" s="36"/>
-      <c r="J141" s="51"/>
-      <c r="K141" s="45"/>
+      <c r="J141" s="55"/>
+      <c r="K141" s="59"/>
     </row>
     <row r="142" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="19">
@@ -5103,8 +5608,8 @@
       <c r="G142" s="35"/>
       <c r="H142" s="13"/>
       <c r="I142" s="36"/>
-      <c r="J142" s="51"/>
-      <c r="K142" s="45"/>
+      <c r="J142" s="55"/>
+      <c r="K142" s="59"/>
     </row>
     <row r="143" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="19">
@@ -5126,8 +5631,8 @@
       <c r="G143" s="35"/>
       <c r="H143" s="13"/>
       <c r="I143" s="36"/>
-      <c r="J143" s="51"/>
-      <c r="K143" s="45"/>
+      <c r="J143" s="55"/>
+      <c r="K143" s="59"/>
     </row>
     <row r="144" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="19">
@@ -5149,8 +5654,8 @@
       <c r="G144" s="35"/>
       <c r="H144" s="13"/>
       <c r="I144" s="36"/>
-      <c r="J144" s="51"/>
-      <c r="K144" s="45"/>
+      <c r="J144" s="55"/>
+      <c r="K144" s="59"/>
     </row>
     <row r="145" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="19">
@@ -5174,12 +5679,16 @@
       <c r="G145" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H145" s="13"/>
-      <c r="I145" s="57" t="s">
+      <c r="H145" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J145" s="50"/>
-      <c r="K145" s="45"/>
+      <c r="J145" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K145" s="59"/>
     </row>
     <row r="146" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="19">
@@ -5203,12 +5712,16 @@
       <c r="G146" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H146" s="13"/>
-      <c r="I146" s="57" t="s">
+      <c r="H146" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J146" s="50"/>
-      <c r="K146" s="45"/>
+      <c r="J146" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K146" s="59"/>
     </row>
     <row r="147" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="19">
@@ -5229,11 +5742,17 @@
       <c r="F147" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="G147" s="35"/>
-      <c r="H147" s="13"/>
-      <c r="I147" s="36"/>
-      <c r="J147" s="50"/>
-      <c r="K147" s="45"/>
+      <c r="G147" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H147" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J147" s="54"/>
+      <c r="K147" s="59"/>
       <c r="L147" s="22"/>
       <c r="M147" s="22"/>
     </row>
@@ -5257,8 +5776,8 @@
       <c r="G148" s="35"/>
       <c r="H148" s="13"/>
       <c r="I148" s="36"/>
-      <c r="J148" s="51"/>
-      <c r="K148" s="45"/>
+      <c r="J148" s="55"/>
+      <c r="K148" s="59"/>
       <c r="L148" s="22"/>
       <c r="M148" s="22"/>
     </row>
@@ -5282,9 +5801,9 @@
       <c r="G149" s="35"/>
       <c r="H149" s="13"/>
       <c r="I149" s="36"/>
-      <c r="J149" s="51"/>
-      <c r="K149" s="45"/>
-      <c r="L149" s="41" t="s">
+      <c r="J149" s="55"/>
+      <c r="K149" s="59"/>
+      <c r="L149" s="40" t="s">
         <v>11</v>
       </c>
       <c r="M149" s="23">
@@ -5312,9 +5831,9 @@
       <c r="G150" s="35"/>
       <c r="H150" s="13"/>
       <c r="I150" s="36"/>
-      <c r="J150" s="51"/>
-      <c r="K150" s="45"/>
-      <c r="L150" s="42" t="s">
+      <c r="J150" s="55"/>
+      <c r="K150" s="59"/>
+      <c r="L150" s="41" t="s">
         <v>12</v>
       </c>
       <c r="M150" s="24">
@@ -5342,14 +5861,14 @@
       <c r="G151" s="35"/>
       <c r="H151" s="13"/>
       <c r="I151" s="36"/>
-      <c r="J151" s="51"/>
-      <c r="K151" s="45"/>
-      <c r="L151" s="43" t="s">
+      <c r="J151" s="55"/>
+      <c r="K151" s="59"/>
+      <c r="L151" s="42" t="s">
         <v>16</v>
       </c>
       <c r="M151" s="25">
         <f>COUNTIF(F2:F183,"Schreiber ")</f>
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5372,11 +5891,11 @@
       <c r="G152" s="35"/>
       <c r="H152" s="13"/>
       <c r="I152" s="36"/>
-      <c r="J152" s="51"/>
-      <c r="K152" s="45"/>
+      <c r="J152" s="55"/>
+      <c r="K152" s="59"/>
       <c r="M152" s="10">
         <f>SUM(M147:M151)</f>
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5401,10 +5920,18 @@
       <c r="G153" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H153" s="13"/>
-      <c r="I153" s="36"/>
-      <c r="J153" s="50"/>
-      <c r="K153" s="45"/>
+      <c r="H153" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I153" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J153" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K153" s="65" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="154" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="19">
@@ -5428,10 +5955,18 @@
       <c r="G154" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H154" s="13"/>
-      <c r="I154" s="36"/>
-      <c r="J154" s="51"/>
-      <c r="K154" s="45"/>
+      <c r="H154" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J154" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K154" s="65" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="155" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="19">
@@ -5455,10 +5990,18 @@
       <c r="G155" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H155" s="13"/>
-      <c r="I155" s="36"/>
-      <c r="J155" s="51"/>
-      <c r="K155" s="45"/>
+      <c r="H155" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I155" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J155" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="K155" s="65" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="156" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="19">
@@ -5480,8 +6023,8 @@
       <c r="G156" s="35"/>
       <c r="H156" s="13"/>
       <c r="I156" s="36"/>
-      <c r="J156" s="51"/>
-      <c r="K156" s="45"/>
+      <c r="J156" s="55"/>
+      <c r="K156" s="59"/>
     </row>
     <row r="157" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="19">
@@ -5503,8 +6046,8 @@
       <c r="G157" s="35"/>
       <c r="H157" s="13"/>
       <c r="I157" s="36"/>
-      <c r="J157" s="51"/>
-      <c r="K157" s="45"/>
+      <c r="J157" s="55"/>
+      <c r="K157" s="59"/>
     </row>
     <row r="158" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="19">
@@ -5526,8 +6069,8 @@
       <c r="G158" s="35"/>
       <c r="H158" s="13"/>
       <c r="I158" s="36"/>
-      <c r="J158" s="51"/>
-      <c r="K158" s="45"/>
+      <c r="J158" s="55"/>
+      <c r="K158" s="59"/>
     </row>
     <row r="159" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="19">
@@ -5549,8 +6092,8 @@
       <c r="G159" s="35"/>
       <c r="H159" s="13"/>
       <c r="I159" s="36"/>
-      <c r="J159" s="51"/>
-      <c r="K159" s="45"/>
+      <c r="J159" s="55"/>
+      <c r="K159" s="59"/>
     </row>
     <row r="160" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="19">
@@ -5572,8 +6115,8 @@
       <c r="G160" s="35"/>
       <c r="H160" s="13"/>
       <c r="I160" s="36"/>
-      <c r="J160" s="51"/>
-      <c r="K160" s="45"/>
+      <c r="J160" s="55"/>
+      <c r="K160" s="59"/>
     </row>
     <row r="161" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="19">
@@ -5597,12 +6140,16 @@
       <c r="G161" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H161" s="13"/>
-      <c r="I161" s="57" t="s">
+      <c r="H161" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I161" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J161" s="51"/>
-      <c r="K161" s="45"/>
+      <c r="J161" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K161" s="59"/>
     </row>
     <row r="162" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="19">
@@ -5626,12 +6173,16 @@
       <c r="G162" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H162" s="13"/>
-      <c r="I162" s="57" t="s">
+      <c r="H162" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I162" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J162" s="51"/>
-      <c r="K162" s="45"/>
+      <c r="J162" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K162" s="59"/>
     </row>
     <row r="163" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="19">
@@ -5653,8 +6204,8 @@
       <c r="G163" s="35"/>
       <c r="H163" s="13"/>
       <c r="I163" s="36"/>
-      <c r="J163" s="51"/>
-      <c r="K163" s="45"/>
+      <c r="J163" s="55"/>
+      <c r="K163" s="59"/>
     </row>
     <row r="164" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="19">
@@ -5676,8 +6227,8 @@
       <c r="G164" s="35"/>
       <c r="H164" s="13"/>
       <c r="I164" s="36"/>
-      <c r="J164" s="51"/>
-      <c r="K164" s="45"/>
+      <c r="J164" s="55"/>
+      <c r="K164" s="59"/>
     </row>
     <row r="165" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="19">
@@ -5699,8 +6250,8 @@
       <c r="G165" s="35"/>
       <c r="H165" s="13"/>
       <c r="I165" s="36"/>
-      <c r="J165" s="51"/>
-      <c r="K165" s="45"/>
+      <c r="J165" s="55"/>
+      <c r="K165" s="59"/>
     </row>
     <row r="166" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="19">
@@ -5722,8 +6273,8 @@
       <c r="G166" s="35"/>
       <c r="H166" s="13"/>
       <c r="I166" s="36"/>
-      <c r="J166" s="51"/>
-      <c r="K166" s="45"/>
+      <c r="J166" s="55"/>
+      <c r="K166" s="59"/>
     </row>
     <row r="167" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="19">
@@ -5745,8 +6296,8 @@
       <c r="G167" s="35"/>
       <c r="H167" s="13"/>
       <c r="I167" s="36"/>
-      <c r="J167" s="51"/>
-      <c r="K167" s="45"/>
+      <c r="J167" s="55"/>
+      <c r="K167" s="59"/>
     </row>
     <row r="168" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="19">
@@ -5768,8 +6319,8 @@
       <c r="G168" s="35"/>
       <c r="H168" s="13"/>
       <c r="I168" s="36"/>
-      <c r="J168" s="51"/>
-      <c r="K168" s="45"/>
+      <c r="J168" s="55"/>
+      <c r="K168" s="59"/>
     </row>
     <row r="169" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="19">
@@ -5790,11 +6341,19 @@
       <c r="F169" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="G169" s="35"/>
-      <c r="H169" s="13"/>
-      <c r="I169" s="36"/>
-      <c r="J169" s="51"/>
-      <c r="K169" s="45"/>
+      <c r="G169" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H169" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I169" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J169" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K169" s="59"/>
     </row>
     <row r="170" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="19">
@@ -5815,11 +6374,19 @@
       <c r="F170" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="G170" s="35"/>
-      <c r="H170" s="13"/>
-      <c r="I170" s="36"/>
-      <c r="J170" s="51"/>
-      <c r="K170" s="45"/>
+      <c r="G170" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H170" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I170" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J170" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K170" s="65"/>
     </row>
     <row r="171" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="19">
@@ -5841,8 +6408,8 @@
       <c r="G171" s="35"/>
       <c r="H171" s="13"/>
       <c r="I171" s="36"/>
-      <c r="J171" s="51"/>
-      <c r="K171" s="45"/>
+      <c r="J171" s="55"/>
+      <c r="K171" s="59"/>
     </row>
     <row r="172" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="19">
@@ -5864,8 +6431,8 @@
       <c r="G172" s="35"/>
       <c r="H172" s="13"/>
       <c r="I172" s="36"/>
-      <c r="J172" s="51"/>
-      <c r="K172" s="45"/>
+      <c r="J172" s="55"/>
+      <c r="K172" s="59"/>
     </row>
     <row r="173" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="19">
@@ -5887,8 +6454,8 @@
       <c r="G173" s="35"/>
       <c r="H173" s="13"/>
       <c r="I173" s="36"/>
-      <c r="J173" s="51"/>
-      <c r="K173" s="45"/>
+      <c r="J173" s="55"/>
+      <c r="K173" s="59"/>
     </row>
     <row r="174" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="19">
@@ -5910,8 +6477,8 @@
       <c r="G174" s="35"/>
       <c r="H174" s="13"/>
       <c r="I174" s="36"/>
-      <c r="J174" s="51"/>
-      <c r="K174" s="45"/>
+      <c r="J174" s="55"/>
+      <c r="K174" s="59"/>
     </row>
     <row r="175" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="19">
@@ -5933,8 +6500,8 @@
       <c r="G175" s="35"/>
       <c r="H175" s="13"/>
       <c r="I175" s="36"/>
-      <c r="J175" s="51"/>
-      <c r="K175" s="45"/>
+      <c r="J175" s="55"/>
+      <c r="K175" s="59"/>
     </row>
     <row r="176" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="19">
@@ -5956,8 +6523,8 @@
       <c r="G176" s="35"/>
       <c r="H176" s="13"/>
       <c r="I176" s="36"/>
-      <c r="J176" s="51"/>
-      <c r="K176" s="45"/>
+      <c r="J176" s="55"/>
+      <c r="K176" s="59"/>
     </row>
     <row r="177" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="19">
@@ -5978,11 +6545,19 @@
       <c r="F177" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="G177" s="35"/>
-      <c r="H177" s="13"/>
-      <c r="I177" s="36"/>
-      <c r="J177" s="51"/>
-      <c r="K177" s="45"/>
+      <c r="G177" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H177" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I177" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J177" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K177" s="59"/>
     </row>
     <row r="178" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="19">
@@ -6006,12 +6581,16 @@
       <c r="G178" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H178" s="13"/>
-      <c r="I178" s="57" t="s">
+      <c r="H178" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I178" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="J178" s="51"/>
-      <c r="K178" s="45"/>
+      <c r="J178" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K178" s="55"/>
     </row>
     <row r="179" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="19">
@@ -6023,18 +6602,26 @@
       <c r="C179" s="6">
         <v>0</v>
       </c>
-      <c r="D179" s="6">
+      <c r="D179" s="64">
         <v>0</v>
       </c>
       <c r="E179" s="7">
         <v>0</v>
       </c>
-      <c r="F179" s="29"/>
-      <c r="G179" s="35"/>
-      <c r="H179" s="13"/>
+      <c r="F179" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G179" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H179" s="45" t="s">
+        <v>17</v>
+      </c>
       <c r="I179" s="36"/>
-      <c r="J179" s="51"/>
-      <c r="K179" s="45"/>
+      <c r="J179" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K179" s="59"/>
     </row>
     <row r="180" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="19">
@@ -6046,18 +6633,26 @@
       <c r="C180" s="6">
         <v>0</v>
       </c>
-      <c r="D180" s="6">
+      <c r="D180" s="64">
         <v>0</v>
       </c>
       <c r="E180" s="7">
         <v>0</v>
       </c>
-      <c r="F180" s="29"/>
-      <c r="G180" s="35"/>
-      <c r="H180" s="13"/>
+      <c r="F180" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G180" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H180" s="45" t="s">
+        <v>17</v>
+      </c>
       <c r="I180" s="36"/>
-      <c r="J180" s="51"/>
-      <c r="K180" s="45"/>
+      <c r="J180" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K180" s="59"/>
     </row>
     <row r="181" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="19">
@@ -6069,18 +6664,26 @@
       <c r="C181" s="6">
         <v>0</v>
       </c>
-      <c r="D181" s="6">
+      <c r="D181" s="64">
         <v>0</v>
       </c>
       <c r="E181" s="7">
         <v>0</v>
       </c>
-      <c r="F181" s="29"/>
-      <c r="G181" s="35"/>
-      <c r="H181" s="13"/>
+      <c r="F181" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G181" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H181" s="45" t="s">
+        <v>17</v>
+      </c>
       <c r="I181" s="36"/>
-      <c r="J181" s="51"/>
-      <c r="K181" s="45"/>
+      <c r="J181" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K181" s="59"/>
     </row>
     <row r="182" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="19">
@@ -6102,8 +6705,8 @@
       <c r="G182" s="35"/>
       <c r="H182" s="13"/>
       <c r="I182" s="36"/>
-      <c r="J182" s="51"/>
-      <c r="K182" s="45"/>
+      <c r="J182" s="55"/>
+      <c r="K182" s="59"/>
     </row>
     <row r="183" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A183" s="20">
@@ -6124,9 +6727,9 @@
       <c r="F183" s="33"/>
       <c r="G183" s="37"/>
       <c r="H183" s="38"/>
-      <c r="I183" s="58"/>
-      <c r="J183" s="52"/>
-      <c r="K183" s="47"/>
+      <c r="I183" s="50"/>
+      <c r="J183" s="56"/>
+      <c r="K183" s="62"/>
     </row>
     <row r="184" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A184" s="17" t="s">
@@ -6157,72 +6760,208 @@
       <c r="I184" s="12"/>
       <c r="J184" s="21">
         <f>COUNTIF(J1:J183,"True")</f>
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:J33">
-    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="False">
+    <cfRule type="containsText" dxfId="49" priority="62" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",G2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="48" priority="61" operator="containsText" text="False">
       <formula>NOT(ISERROR(SEARCH("False",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="6" stopIfTrue="1" operator="containsText" text="True">
-      <formula>NOT(ISERROR(SEARCH("True",G2)))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:K1 G34:G36 G37:J41 G42:G44 G45:J49 G50:G52 I50:J52 G53:J57 G58:G60 G61:J64 G65:G67 I65:J67 G68:J72 G76:J80 G81:G83 G84:J88 G89:G91 G92:J96 G97:G99 G100:J104 G105:G107 G108:J112 G113:G115 G116:J120 G121:G123 G124:J128 G129:G131 G132:J136 G137:G139 G140:J144 G145:G147 I145:I147 I147:J147 G148:J152 G153:G155 G156:J160 G161:G162 G163:J168 G169:G170 G171:J176 G182:J183 G177:G181 I179:I181">
+    <cfRule type="containsText" dxfId="47" priority="78" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",G1)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:K1 G34:G36 G37:J41 G42:G44 G45:J49 G50:G52 I50:J52 G53:J57 G58:G60 G61:J64 G65:G67 I65:J67 G68:J72 G76:J80 G81:G83 I81:J83 G84:J88 G89:G91 I89:J91 G92:J96 G97:G99 I97:J99 G100:J104 G105:G107 I105:J107 G108:J183">
-    <cfRule type="containsText" dxfId="13" priority="21" operator="containsText" text="False">
+    <cfRule type="containsText" dxfId="46" priority="77" operator="containsText" text="False">
       <formula>NOT(ISERROR(SEARCH("False",G1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="22" stopIfTrue="1" operator="containsText" text="True">
-      <formula>NOT(ISERROR(SEARCH("True",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="False">
+    <cfRule type="containsText" dxfId="45" priority="60" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",H34)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="44" priority="59" operator="containsText" text="False">
       <formula>NOT(ISERROR(SEARCH("False",H34)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="4" stopIfTrue="1" operator="containsText" text="True">
-      <formula>NOT(ISERROR(SEARCH("True",H34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H58:H59">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="False">
+    <cfRule type="containsText" dxfId="43" priority="58" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",H58)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="42" priority="57" operator="containsText" text="False">
       <formula>NOT(ISERROR(SEARCH("False",H58)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="2" stopIfTrue="1" operator="containsText" text="True">
-      <formula>NOT(ISERROR(SEARCH("True",H58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34:J36">
-    <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="False">
+    <cfRule type="containsText" dxfId="41" priority="70" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I34)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="69" operator="containsText" text="False">
       <formula>NOT(ISERROR(SEARCH("False",I34)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="14" stopIfTrue="1" operator="containsText" text="True">
-      <formula>NOT(ISERROR(SEARCH("True",I34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I42:J44">
-    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="False">
+    <cfRule type="containsText" dxfId="39" priority="68" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I42)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="38" priority="67" operator="containsText" text="False">
       <formula>NOT(ISERROR(SEARCH("False",I42)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="12" stopIfTrue="1" operator="containsText" text="True">
-      <formula>NOT(ISERROR(SEARCH("True",I42)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I58:J60">
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="False">
+    <cfRule type="containsText" dxfId="37" priority="66" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I58)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="65" operator="containsText" text="False">
       <formula>NOT(ISERROR(SEARCH("False",I58)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="10" stopIfTrue="1" operator="containsText" text="True">
-      <formula>NOT(ISERROR(SEARCH("True",I58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I73:J75">
-    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="False">
+    <cfRule type="containsText" dxfId="35" priority="64" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I73)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="63" operator="containsText" text="False">
       <formula>NOT(ISERROR(SEARCH("False",I73)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="8" stopIfTrue="1" operator="containsText" text="True">
-      <formula>NOT(ISERROR(SEARCH("True",I73)))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I81:J83">
+    <cfRule type="containsText" dxfId="33" priority="52" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I81)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="32" priority="51" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I81)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I89:J91">
+    <cfRule type="containsText" dxfId="31" priority="50" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I89)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="30" priority="49" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I89)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I97:J99">
+    <cfRule type="containsText" dxfId="29" priority="44" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I97)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="43" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I97)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I105:J107">
+    <cfRule type="containsText" dxfId="27" priority="42" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I105)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="26" priority="41" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I105)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I113:J115">
+    <cfRule type="containsText" dxfId="25" priority="36" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I113)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="35" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I113)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I121:J123">
+    <cfRule type="containsText" dxfId="23" priority="34" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I121)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="33" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I121)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I129:J131">
+    <cfRule type="containsText" dxfId="21" priority="24" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I129)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="23" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I129)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I137:J139">
+    <cfRule type="containsText" dxfId="19" priority="30" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I137)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="29" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I137)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I153:J155">
+    <cfRule type="containsText" dxfId="17" priority="22" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I153)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="21" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I153)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I161:J162">
+    <cfRule type="containsText" dxfId="15" priority="20" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I161)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="19" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I161)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I169:J170">
+    <cfRule type="containsText" dxfId="13" priority="16" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I169)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="15" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I169)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I177:J178">
+    <cfRule type="containsText" dxfId="11" priority="10" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",I177)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",I177)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J145:J146">
+    <cfRule type="containsText" dxfId="9" priority="26" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",J145)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="25" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",J145)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K178">
+    <cfRule type="containsText" dxfId="7" priority="8" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",K178)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",K178)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J179">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",J179)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="6" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",J179)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J180">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",J180)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="4" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",J180)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J181">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="False">
+      <formula>NOT(ISERROR(SEARCH("False",J181)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" stopIfTrue="1" operator="containsText" text="True">
+      <formula>NOT(ISERROR(SEARCH("True",J181)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
